--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712043</v>
+        <v>113714271</v>
       </c>
       <c r="B2" t="n">
         <v>81944</v>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714271</v>
+        <v>113714157</v>
       </c>
       <c r="B2" t="n">
         <v>81944</v>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714157</v>
+        <v>113712043</v>
       </c>
       <c r="B2" t="n">
         <v>81944</v>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712043</v>
+        <v>113714157</v>
       </c>
       <c r="B2" t="n">
         <v>81944</v>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,6 +1304,103 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131736076</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fäbodbäcken Syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>652069</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7031446</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>131736076</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>131736076</v>
       </c>
       <c r="B8" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>131736076</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>131736076</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>131736076</v>
       </c>
       <c r="B8" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>131736076</v>
       </c>
       <c r="B8" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>131736076</v>
       </c>
       <c r="B8" t="n">
-        <v>91868</v>
+        <v>91904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>131736076</v>
       </c>
       <c r="B8" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 41267-2021 artfynd.xlsx
+++ b/artfynd/A 41267-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739555</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712043</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677314</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120676713</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677070</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677148</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677205</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677595</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,8 +1733,25 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712042</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>